--- a/01_analyses_mask-PA/results/SoIB_summaries.xlsx
+++ b/01_analyses_mask-PA/results/SoIB_summaries.xlsx
@@ -393,16 +393,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="3">
@@ -412,16 +412,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D3">
-        <v>13.5</v>
+        <v>11.7</v>
       </c>
       <c r="E3">
-        <v>15.3</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C4">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="D4">
-        <v>63.5</v>
+        <v>65</v>
       </c>
       <c r="E4">
-        <v>75</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="5">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5">
-        <v>15.6</v>
+        <v>12.6</v>
       </c>
       <c r="E5">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="6">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6">
-        <v>6.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E6">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C7">
-        <v>320</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C8">
-        <v>313</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C3">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="C4">
-        <v>124</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5">
@@ -763,16 +763,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C2">
-        <v>7.8</v>
+        <v>12.6</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2">
-        <v>26.7</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="3">
@@ -782,16 +782,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>3.3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -801,16 +801,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C4">
-        <v>85.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E4">
-        <v>70</v>
+        <v>46.7</v>
       </c>
     </row>
   </sheetData>

--- a/01_analyses_mask-PA/results/SoIB_summaries.xlsx
+++ b/01_analyses_mask-PA/results/SoIB_summaries.xlsx
@@ -396,13 +396,13 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D2">
         <v>1.9</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="3">
@@ -412,16 +412,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>23</v>
       </c>
       <c r="D3">
-        <v>12.6</v>
+        <v>11.7</v>
       </c>
       <c r="E3">
-        <v>15.3</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="4">
@@ -434,13 +434,13 @@
         <v>67</v>
       </c>
       <c r="C4">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D4">
         <v>65</v>
       </c>
       <c r="E4">
-        <v>71.3</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="5">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>14.6</v>
+        <v>12.6</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="6">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>5.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E6">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C7">
-        <v>294</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C8">
-        <v>313</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="3">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C3">
         <v>103</v>
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="C4">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5">
@@ -763,16 +763,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C2">
-        <v>15.5</v>
+        <v>12.6</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E2">
-        <v>53.3</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="3">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="D3">
         <v>3</v>
@@ -801,16 +801,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C4">
-        <v>75.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E4">
-        <v>36.7</v>
+        <v>46.7</v>
       </c>
     </row>
   </sheetData>

--- a/01_analyses_mask-PA/results/SoIB_summaries.xlsx
+++ b/01_analyses_mask-PA/results/SoIB_summaries.xlsx
@@ -393,16 +393,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>1.9</v>
+        <v>28</v>
       </c>
       <c r="E2">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="3">
@@ -412,16 +412,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="C3">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D3">
-        <v>11.7</v>
+        <v>31.1</v>
       </c>
       <c r="E3">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="C4">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="D4">
-        <v>65</v>
+        <v>27.3</v>
       </c>
       <c r="E4">
-        <v>75.3</v>
+        <v>80.09999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>12.6</v>
+        <v>7.5</v>
       </c>
       <c r="E5">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="6">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>8.699999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="E6">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>207</v>
+        <v>150</v>
       </c>
       <c r="C7">
-        <v>306</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="C8">
-        <v>304</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>756</v>
+        <v>747</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C3">
-        <v>103</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="C4">
-        <v>146</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5">
@@ -763,16 +763,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C2">
-        <v>12.6</v>
+        <v>22.3</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>43.3</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="3">
@@ -782,16 +782,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>7.8</v>
+        <v>3.9</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -801,16 +801,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C4">
-        <v>79.59999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4">
-        <v>46.7</v>
+        <v>37.5</v>
       </c>
     </row>
   </sheetData>
